--- a/apps/web/public/samples/A/statement.xlsx
+++ b/apps/web/public/samples/A/statement.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>KAMOLA ISMOILOV</t>
+          <t>KAMOLA ISMOILOVA</t>
         </is>
       </c>
     </row>
